--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2018_la_araucania.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:39</t>
+    <t xml:space="preserve">2026-10-05 21:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
